--- a/stories/arbres/ATOM-SOC.TRA.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa et Sami vont à la gare. Sami tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Le sol vibre un peu. Papa dit : c'est un train. C'est le nom du véhicule. Sami répète : un train. Ils montent avec papa. Sami s'assoit près de papa. Le train roule. Sami entend le bruit. Par la fenêtre, Sami voit le ciel. Un avion passe. L'avion fait un grand trait blanc. Papa dit : c'est un avion. C'est un autre nom de véhicule. Sami dit : un avion. Plus loin, il y a une rivière. Un bateau glisse sur l'eau. Papa dit : c'est un bateau. Sami dit : un bateau. Train, avion, bateau. Sami nomme. Il reste avec papa.</t>
+          <t>Papa et Sami vont à la gare. Sami tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Le sol vibre un peu. C'est un train. C'est le nom du véhicule. Sami répète : un train. Ils montent avec papa. Sami s'assoit près de papa. Le train roule. Sami entend le bruit. Par la fenêtre, Sami voit le ciel. Un avion passe. L'avion fait un grand trait blanc. C'est un avion. C'est un autre nom de véhicule. Un avion. Plus loin, il y a une rivière. Un bateau glisse sur l'eau. C'est un bateau. Un bateau. Train, avion, bateau. Sami nomme. Il reste avec papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Papa et Sami vont à la gare. Sami tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Le sol vibre un peu.
+papa|C'est un train. C'est le nom du véhicule.
+narrateur|Sami répète : un train. Ils montent avec papa. Sami s'assoit près de papa. Le train roule. Sami entend le bruit. Par la fenêtre, Sami voit le ciel. Un avion passe. L'avion fait un grand trait blanc.
+papa|C'est un avion. C'est un autre nom de véhicule.
+enfant-m|Un avion. Plus loin, il y a une rivière.
+narrateur|Un bateau glisse sur l'eau.
+papa|C'est un bateau.
+enfant-m|Un bateau. Train, avion, bateau.
+narrateur|Sami nomme. Il reste avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Sami nomme un véhicule. Lequel ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a dit le nom du véhicule. Train. Avion. Bateau. Il est resté avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1838,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le train s'arrête. Sami donne la main à papa. Ils descendent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2005,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Sami nomme. Il reste avec papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Sami nomme un véhicule. Lequel ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Sami a dit le nom du véhicule. Train. Avion. Bateau. Il est resté avec papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1851,7 @@
           <t>narrateur|Le train s'arrête. Sami donne la main à papa. Ils descendent ensemble.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le train de Sami</t>
+          <t>La rivière du train de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut voir la rivière par le hublot du train. Le goûter roule. Ils restent assis avec papa et le rattrapent. L'eau apparaît.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa et Sami vont à la gare. Sami tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Le sol vibre un peu. C'est un train. C'est le nom du véhicule. Sami répète : un train. Ils montent avec papa. Sami s'assoit près de papa. Le train roule. Sami entend le bruit. Par la fenêtre, Sami voit le ciel. Un avion passe. L'avion fait un grand trait blanc. C'est un avion. C'est un autre nom de véhicule. Un avion. Plus loin, il y a une rivière. Un bateau glisse sur l'eau. C'est un bateau. Un bateau. Train, avion, bateau. Sami nomme. Il reste avec papa.</t>
+          <t>Le quai sent le fer et le vent. Une valise passe tout doucement. Le banc du quai est froid. Papa tient un petit sac brun. Raphaël vit ici, avec papa. Tu entends le quai, Raphaël ? Ça sent le fer. Oui. Le train arrive bientôt. En ce moment, ils attendent. Raphaël pose les mains sur le bois. Je veux voir la rivière. On la verra par la fenêtre. Dans le train. Un bruit s'approche, tout long. Le sol vibre un peu. Tchou tchou. C'est le train. On reste avec papa. Ils montent ensemble. Raphaël donne la main. On s'assoit ici. Sur le banc. Le banc du train est chaud. Un hublot rond montre le quai. Le hublot ! On reste assis. Avec un adulte. Le train part, tout doucement. Les maisons glissent. La rivière ? Bientôt. Papa pose le sac brun. Le goûter est dedans. Une pomme roule sur le banc. Elle part ! On reste assis. On la rattrape d'ici. Raphaël reste sur le banc. Il tend la main. La pomme arrive vers lui. Je l'ai ! Bravo. Assis, avec papa. La pomme est un peu froide. Raphaël la remet dans le sac. Tu as vu le hublot ? Oui. Dehors, les champs sont verts. Un ruban brille, tout loin. L'eau ! La rivière.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa et Sami vont à la gare. Sami tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Le sol vibre un peu. Papa dit : c'est un train. C'est le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Sami répète : un train. Ils montent avec papa. Sami s'assoit près de papa. Le train roule. Sami entend le bruit. Par la fenêtre, Sami voit le ciel. Un avion passe. L'avion fait un grand trait blanc. Papa dit : c'est un avion. C'est un autre nom de véhicule. Sami dit : un avion. Plus loin, il y a une rivière. Un bateau glisse sur l'eau. Papa dit : c'est un bateau. Sami dit : un bateau. Train, avion, bateau. Sami nomme. Il reste avec papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le quai sent le fer et le vent. Une valise passe tout doucement. Le banc du quai est froid. Papa tient un petit sac brun. Raphaël vit ici, avec papa. Tu entends le quai, Raphaël ? Ça sent le fer. Oui. Le train arrive bientôt. En ce moment, ils attendent. Raphaël pose les mains sur le bois. Je veux voir la rivière. On la verra par la fenêtre. Dans le train. Un bruit s'approche, tout long. Le sol vibre un peu. Tchou tchou. C'est le train. On reste avec papa. Ils montent ensemble. Raphaël donne la main. On s'assoit ici. Sur le banc. Le banc du train est chaud. Un hublot rond montre le quai. Le hublot ! On reste assis. Avec un adulte. Le train part, tout doucement. Les maisons glissent. La rivière ? Bientôt. Papa pose le sac brun. Le goûter est dedans. Une pomme roule sur le banc. Elle part ! On reste assis. On la rattrape d'ici. Raphaël reste sur le banc. Il tend la main. La pomme arrive vers lui. Je l'ai ! Bravo. Assis, avec papa. La pomme est un peu froide. Raphaël la remet dans le sac. Tu as vu le hublot ? Oui. Dehors, les champs sont verts. Un ruban brille, tout loin. L'eau ! La rivière.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,18 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Papa et Sami vont à la gare. Sami tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Le sol vibre un peu.
-papa|C'est un train. C'est le nom du véhicule.
-narrateur|Sami répète : un train. Ils montent avec papa. Sami s'assoit près de papa. Le train roule. Sami entend le bruit. Par la fenêtre, Sami voit le ciel. Un avion passe. L'avion fait un grand trait blanc.
-papa|C'est un avion. C'est un autre nom de véhicule.
-enfant-m|Un avion. Plus loin, il y a une rivière.
-narrateur|Un bateau glisse sur l'eau.
-papa|C'est un bateau.
-enfant-m|Un bateau. Train, avion, bateau.
-narrateur|Sami nomme. Il reste avec papa.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le quai sent le fer et le vent.
+narrateur|Une valise passe tout doucement.
+narrateur|Le banc du quai est froid.
+narrateur|Papa tient un petit sac brun.
+narrateur|Raphaël vit ici, avec papa.
+papa|Tu entends le quai, Raphaël ?
+enfant-m|Ça sent le fer.
+papa|Oui.
+papa|Le train arrive bientôt.
+narrateur|En ce moment, ils attendent.
+narrateur|Raphaël pose les mains sur le bois.
+enfant-m|Je veux voir la rivière.
+papa|On la verra par la fenêtre.
+papa|Dans le train.
+narrateur|Un bruit s'approche, tout long.
+narrateur|Le sol vibre un peu.
+enfant-m|Tchou tchou.
+papa|C'est le train.
+papa|On reste avec papa.
+narrateur|Ils montent ensemble.
+narrateur|Raphaël donne la main.
+papa|On s'assoit ici.
+papa|Sur le banc.
+narrateur|Le banc du train est chaud.
+narrateur|Un hublot rond montre le quai.
+enfant-m|Le hublot !
+papa|On reste assis.
+papa|Avec un adulte.
+narrateur|Le train part, tout doucement.
+narrateur|Les maisons glissent.
+enfant-m|La rivière ?
+papa|Bientôt.
+narrateur|Papa pose le sac brun.
+narrateur|Le goûter est dedans.
+narrateur|Une pomme roule sur le banc.
+enfant-m|Elle part !
+papa|On reste assis.
+papa|On la rattrape d'ici.
+narrateur|Raphaël reste sur le banc.
+narrateur|Il tend la main.
+narrateur|La pomme arrive vers lui.
+enfant-m|Je l'ai !
+papa|Bravo.
+papa|Assis, avec papa.
+narrateur|La pomme est un peu froide.
+narrateur|Raphaël la remet dans le sac.
+papa|Tu as vu le hublot ?
+enfant-m|Oui.
+narrateur|Dehors, les champs sont verts.
+narrateur|Un ruban brille, tout loin.
+enfant-m|L'eau !
+papa|La rivière.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,12 +1402,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sami nomme un véhicule. Lequel ?</t>
+          <t>Raphaël voyage avec papa. Quel véhicule roule ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sami &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un véhicule. Lequel ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël voyage avec papa. Quel véhicule roule ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1417,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>train</t>
+          <t>le train</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>train | avion | bateau | un train | le train</t>
+          <t>train | le train | un train</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1437,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il a vu un train. Quel véhicule ?</t>
+          <t>C'est le train. Quel véhicule roule ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1486,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1562,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sami nomme un véhicule. Lequel ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël voyage avec papa.
+narrateur|Quel véhicule roule ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami a dit le nom du véhicule. Train. Avion. Bateau. Il est resté avec papa.</t>
+          <t>Le train. Oui, le train. Ils restent assis sur le banc. Le hublot se remplit d'eau. La rivière est large. Tu la voulais. La voilà. L'eau file, très vite. Un pont passe au-dessus. On est dessus ? Oui. On reste assis. Raphaël tient encore la pomme. Puis il la range. Merci, Raphaël. Tu es resté assis. Avec toi. Avec un adulte. Le train fait un bruit rond. Le hublot tremble un peu. Ça chatouille. C'est le pont.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sami a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Train. Avion. Bateau. Il est resté avec papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train. Oui, le train. Ils restent assis sur le banc. Le hublot se remplit d'eau. La rivière est large. Tu la voulais. La voilà. L'eau file, très vite. Un pont passe au-dessus. On est dessus ? Oui. On reste assis. Raphaël tient encore la pomme. Puis il la range. Merci, Raphaël. Tu es resté assis. Avec toi. Avec un adulte. Le train fait un bruit rond. Le hublot tremble un peu. Ça chatouille. C'est le pont.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1597,14 +1651,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1734,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sami a dit le nom du véhicule. Train. Avion. Bateau. Il est resté avec papa.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-m|Le train.
+papa|Oui, le train.
+narrateur|Ils restent assis sur le banc.
+narrateur|Le hublot se remplit d'eau.
+enfant-m|La rivière est large.
+papa|Tu la voulais.
+papa|La voilà.
+narrateur|L'eau file, très vite.
+narrateur|Un pont passe au-dessus.
+enfant-m|On est dessus ?
+papa|Oui.
+papa|On reste assis.
+narrateur|Raphaël tient encore la pomme.
+narrateur|Puis il la range.
+papa|Merci, Raphaël.
+papa|Tu es resté assis.
+enfant-m|Avec toi.
+papa|Avec un adulte.
+narrateur|Le train fait un bruit rond.
+narrateur|Le hublot tremble un peu.
+enfant-m|Ça chatouille.
+papa|C'est le pont.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête. Sami donne la main à papa. Ils descendent ensemble.</t>
+          <t>Tu as fini de regarder l'eau ? Encore un peu. La rivière devient plus étroite. Des arbres la cachent. Elle part. Elle suit le train, un moment. Raphaël pose le front au hublot. Le verre est frais. Le train. Et la rivière. Oui. Le sac brun reste entre eux. La pomme ne roule plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le train s'arrête. Sami donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa. Ils descendent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu as fini de regarder l'eau ? Encore un peu. La rivière devient plus étroite. Des arbres la cachent. Elle part. Elle suit le train, un moment. Raphaël pose le front au hublot. Le verre est frais. Le train. Et la rivière. Oui. Le sac brun reste entre eux. La pomme ne roule plus.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,14 +1843,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1922,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le train s'arrête. Sami donne la main à papa. Ils descendent ensemble.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>papa|Tu as fini de regarder l'eau ?
+enfant-m|Encore un peu.
+narrateur|La rivière devient plus étroite.
+narrateur|Des arbres la cachent.
+enfant-m|Elle part.
+papa|Elle suit le train, un moment.
+narrateur|Raphaël pose le front au hublot.
+narrateur|Le verre est frais.
+enfant-m|Le train.
+enfant-m|Et la rivière.
+papa|Oui.
+narrateur|Le sac brun reste entre eux.
+narrateur|La pomme ne roule plus.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc garde encore le sac. Le hublot redevient vert. J'ai vu l'eau. Assis, avec papa. Le train continue, tout rond.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le banc garde encore le sac. Le hublot redevient vert. J'ai vu l'eau. Assis, avec papa. Le train continue, tout rond.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1937,14 +2022,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2101,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le banc garde encore le sac.
+narrateur|Le hublot redevient vert.
+enfant-m|J'ai vu l'eau.
+papa|Assis, avec papa.
+narrateur|Le train continue, tout rond.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gare et train</t>
+          <t>quai puis banc du train</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sami, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
